--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769880</v>
+        <v>129769232</v>
       </c>
       <c r="B6" t="n">
         <v>58106</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511515</v>
+        <v>511608</v>
       </c>
       <c r="R6" t="n">
-        <v>6294373</v>
+        <v>6294473</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1229,22 +1229,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769878</v>
+        <v>129769880</v>
       </c>
       <c r="B7" t="n">
         <v>58106</v>
@@ -1315,14 +1315,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511624</v>
+        <v>511515</v>
       </c>
       <c r="R7" t="n">
-        <v>6294438</v>
+        <v>6294373</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769232</v>
+        <v>129769878</v>
       </c>
       <c r="B8" t="n">
         <v>58106</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511608</v>
+        <v>511624</v>
       </c>
       <c r="R8" t="n">
-        <v>6294473</v>
+        <v>6294438</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769866</v>
+        <v>129769232</v>
       </c>
       <c r="B5" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511622</v>
+        <v>511608</v>
       </c>
       <c r="R5" t="n">
-        <v>6294525</v>
+        <v>6294473</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769232</v>
+        <v>129769880</v>
       </c>
       <c r="B6" t="n">
         <v>58106</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511608</v>
+        <v>511515</v>
       </c>
       <c r="R6" t="n">
-        <v>6294473</v>
+        <v>6294373</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1229,22 +1229,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769880</v>
+        <v>129769878</v>
       </c>
       <c r="B7" t="n">
         <v>58106</v>
@@ -1315,14 +1315,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511515</v>
+        <v>511624</v>
       </c>
       <c r="R7" t="n">
-        <v>6294373</v>
+        <v>6294438</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769878</v>
+        <v>129769866</v>
       </c>
       <c r="B8" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511624</v>
+        <v>511622</v>
       </c>
       <c r="R8" t="n">
-        <v>6294438</v>
+        <v>6294525</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129769234</v>
+        <v>129769242</v>
       </c>
       <c r="B3" t="n">
         <v>58106</v>
@@ -835,14 +835,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511589</v>
+        <v>511511</v>
       </c>
       <c r="R3" t="n">
-        <v>6294556</v>
+        <v>6294377</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129769242</v>
+        <v>129769234</v>
       </c>
       <c r="B4" t="n">
         <v>58106</v>
@@ -955,14 +955,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511511</v>
+        <v>511589</v>
       </c>
       <c r="R4" t="n">
-        <v>6294377</v>
+        <v>6294556</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769880</v>
+        <v>129769878</v>
       </c>
       <c r="B6" t="n">
         <v>58106</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511515</v>
+        <v>511624</v>
       </c>
       <c r="R6" t="n">
-        <v>6294373</v>
+        <v>6294438</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769878</v>
+        <v>129769866</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511624</v>
+        <v>511622</v>
       </c>
       <c r="R7" t="n">
-        <v>6294438</v>
+        <v>6294525</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769866</v>
+        <v>129769880</v>
       </c>
       <c r="B8" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,14 +1435,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511622</v>
+        <v>511515</v>
       </c>
       <c r="R8" t="n">
-        <v>6294525</v>
+        <v>6294373</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129769242</v>
+        <v>129769234</v>
       </c>
       <c r="B3" t="n">
         <v>58106</v>
@@ -835,14 +835,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511511</v>
+        <v>511589</v>
       </c>
       <c r="R3" t="n">
-        <v>6294377</v>
+        <v>6294556</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129769234</v>
+        <v>129769242</v>
       </c>
       <c r="B4" t="n">
         <v>58106</v>
@@ -955,14 +955,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511589</v>
+        <v>511511</v>
       </c>
       <c r="R4" t="n">
-        <v>6294556</v>
+        <v>6294377</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769878</v>
+        <v>129769880</v>
       </c>
       <c r="B6" t="n">
         <v>58106</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511624</v>
+        <v>511515</v>
       </c>
       <c r="R6" t="n">
-        <v>6294438</v>
+        <v>6294373</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769866</v>
+        <v>129769878</v>
       </c>
       <c r="B7" t="n">
-        <v>58413</v>
+        <v>58106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511622</v>
+        <v>511624</v>
       </c>
       <c r="R7" t="n">
-        <v>6294525</v>
+        <v>6294438</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769880</v>
+        <v>129769866</v>
       </c>
       <c r="B8" t="n">
-        <v>58106</v>
+        <v>58413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,14 +1435,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511515</v>
+        <v>511622</v>
       </c>
       <c r="R8" t="n">
-        <v>6294373</v>
+        <v>6294525</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769876</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129769234</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129769242</v>
       </c>
       <c r="B4" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769232</v>
+        <v>129769866</v>
       </c>
       <c r="B5" t="n">
-        <v>58106</v>
+        <v>58416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511608</v>
+        <v>511622</v>
       </c>
       <c r="R5" t="n">
-        <v>6294473</v>
+        <v>6294525</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769880</v>
+        <v>129769878</v>
       </c>
       <c r="B6" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511515</v>
+        <v>511624</v>
       </c>
       <c r="R6" t="n">
-        <v>6294373</v>
+        <v>6294438</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769878</v>
+        <v>129769880</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,14 +1315,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511624</v>
+        <v>511515</v>
       </c>
       <c r="R7" t="n">
-        <v>6294438</v>
+        <v>6294373</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769866</v>
+        <v>129769232</v>
       </c>
       <c r="B8" t="n">
-        <v>58413</v>
+        <v>58108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511622</v>
+        <v>511608</v>
       </c>
       <c r="R8" t="n">
-        <v>6294525</v>
+        <v>6294473</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,7 +1518,7 @@
         <v>129769233</v>
       </c>
       <c r="B9" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129769237</v>
       </c>
       <c r="B10" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769866</v>
+        <v>129769232</v>
       </c>
       <c r="B5" t="n">
-        <v>58416</v>
+        <v>58108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511622</v>
+        <v>511608</v>
       </c>
       <c r="R5" t="n">
-        <v>6294525</v>
+        <v>6294473</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769878</v>
+        <v>129769880</v>
       </c>
       <c r="B6" t="n">
         <v>58108</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511624</v>
+        <v>511515</v>
       </c>
       <c r="R6" t="n">
-        <v>6294438</v>
+        <v>6294373</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769880</v>
+        <v>129769878</v>
       </c>
       <c r="B7" t="n">
         <v>58108</v>
@@ -1315,14 +1315,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511515</v>
+        <v>511624</v>
       </c>
       <c r="R7" t="n">
-        <v>6294373</v>
+        <v>6294438</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769232</v>
+        <v>129769866</v>
       </c>
       <c r="B8" t="n">
-        <v>58108</v>
+        <v>58416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511608</v>
+        <v>511622</v>
       </c>
       <c r="R8" t="n">
-        <v>6294473</v>
+        <v>6294525</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769232</v>
+        <v>129769866</v>
       </c>
       <c r="B5" t="n">
-        <v>58108</v>
+        <v>58416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511608</v>
+        <v>511622</v>
       </c>
       <c r="R5" t="n">
-        <v>6294473</v>
+        <v>6294525</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769880</v>
+        <v>129769232</v>
       </c>
       <c r="B6" t="n">
         <v>58108</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511515</v>
+        <v>511608</v>
       </c>
       <c r="R6" t="n">
-        <v>6294373</v>
+        <v>6294473</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1229,22 +1229,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769878</v>
+        <v>129769880</v>
       </c>
       <c r="B7" t="n">
         <v>58108</v>
@@ -1315,14 +1315,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511624</v>
+        <v>511515</v>
       </c>
       <c r="R7" t="n">
-        <v>6294438</v>
+        <v>6294373</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769866</v>
+        <v>129769878</v>
       </c>
       <c r="B8" t="n">
-        <v>58416</v>
+        <v>58108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511622</v>
+        <v>511624</v>
       </c>
       <c r="R8" t="n">
-        <v>6294525</v>
+        <v>6294438</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769876</v>
       </c>
       <c r="B2" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>129769234</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>129769242</v>
       </c>
       <c r="B4" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129769866</v>
       </c>
       <c r="B5" t="n">
-        <v>58416</v>
+        <v>58419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769232</v>
+        <v>129769878</v>
       </c>
       <c r="B6" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511608</v>
+        <v>511624</v>
       </c>
       <c r="R6" t="n">
-        <v>6294473</v>
+        <v>6294438</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1229,22 +1229,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1278,7 @@
         <v>129769880</v>
       </c>
       <c r="B7" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769878</v>
+        <v>129769232</v>
       </c>
       <c r="B8" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511624</v>
+        <v>511608</v>
       </c>
       <c r="R8" t="n">
-        <v>6294438</v>
+        <v>6294473</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,7 +1518,7 @@
         <v>129769233</v>
       </c>
       <c r="B9" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129769237</v>
       </c>
       <c r="B10" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769866</v>
+        <v>129769878</v>
       </c>
       <c r="B5" t="n">
-        <v>58419</v>
+        <v>58111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511622</v>
+        <v>511624</v>
       </c>
       <c r="R5" t="n">
-        <v>6294525</v>
+        <v>6294438</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769878</v>
+        <v>129769880</v>
       </c>
       <c r="B6" t="n">
         <v>58111</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511624</v>
+        <v>511515</v>
       </c>
       <c r="R6" t="n">
-        <v>6294438</v>
+        <v>6294373</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769880</v>
+        <v>129769232</v>
       </c>
       <c r="B7" t="n">
         <v>58111</v>
@@ -1315,14 +1315,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511515</v>
+        <v>511608</v>
       </c>
       <c r="R7" t="n">
-        <v>6294373</v>
+        <v>6294473</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1349,22 +1349,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769232</v>
+        <v>129769866</v>
       </c>
       <c r="B8" t="n">
-        <v>58111</v>
+        <v>58419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511608</v>
+        <v>511622</v>
       </c>
       <c r="R8" t="n">
-        <v>6294473</v>
+        <v>6294525</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769878</v>
+        <v>129769866</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>58419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511624</v>
+        <v>511622</v>
       </c>
       <c r="R5" t="n">
-        <v>6294438</v>
+        <v>6294525</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769880</v>
+        <v>129769878</v>
       </c>
       <c r="B6" t="n">
         <v>58111</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511515</v>
+        <v>511624</v>
       </c>
       <c r="R6" t="n">
-        <v>6294373</v>
+        <v>6294438</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769232</v>
+        <v>129769880</v>
       </c>
       <c r="B7" t="n">
         <v>58111</v>
@@ -1315,14 +1315,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511608</v>
+        <v>511515</v>
       </c>
       <c r="R7" t="n">
-        <v>6294473</v>
+        <v>6294373</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1349,22 +1349,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769866</v>
+        <v>129769232</v>
       </c>
       <c r="B8" t="n">
-        <v>58419</v>
+        <v>58111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511622</v>
+        <v>511608</v>
       </c>
       <c r="R8" t="n">
-        <v>6294525</v>
+        <v>6294473</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769866</v>
+        <v>129769232</v>
       </c>
       <c r="B5" t="n">
-        <v>58419</v>
+        <v>58111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511622</v>
+        <v>511608</v>
       </c>
       <c r="R5" t="n">
-        <v>6294525</v>
+        <v>6294473</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1155,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769878</v>
+        <v>129769880</v>
       </c>
       <c r="B6" t="n">
         <v>58111</v>
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511624</v>
+        <v>511515</v>
       </c>
       <c r="R6" t="n">
-        <v>6294438</v>
+        <v>6294373</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769880</v>
+        <v>129769878</v>
       </c>
       <c r="B7" t="n">
         <v>58111</v>
@@ -1315,14 +1315,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511515</v>
+        <v>511624</v>
       </c>
       <c r="R7" t="n">
-        <v>6294373</v>
+        <v>6294438</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769232</v>
+        <v>129769866</v>
       </c>
       <c r="B8" t="n">
-        <v>58111</v>
+        <v>58419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511608</v>
+        <v>511622</v>
       </c>
       <c r="R8" t="n">
-        <v>6294473</v>
+        <v>6294525</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129769876</v>
       </c>
       <c r="B2" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129769234</v>
+        <v>129769242</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,14 +835,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511589</v>
+        <v>511511</v>
       </c>
       <c r="R3" t="n">
-        <v>6294556</v>
+        <v>6294377</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129769242</v>
+        <v>129769234</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,14 +955,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511511</v>
+        <v>511589</v>
       </c>
       <c r="R4" t="n">
-        <v>6294377</v>
+        <v>6294556</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
         <v>129769232</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769880</v>
+        <v>129769866</v>
       </c>
       <c r="B6" t="n">
-        <v>58111</v>
+        <v>58420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1195,14 +1195,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511515</v>
+        <v>511622</v>
       </c>
       <c r="R6" t="n">
-        <v>6294373</v>
+        <v>6294525</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1278,7 @@
         <v>129769878</v>
       </c>
       <c r="B7" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769866</v>
+        <v>129769880</v>
       </c>
       <c r="B8" t="n">
-        <v>58419</v>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,14 +1435,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511622</v>
+        <v>511515</v>
       </c>
       <c r="R8" t="n">
-        <v>6294525</v>
+        <v>6294373</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,7 +1518,7 @@
         <v>129769233</v>
       </c>
       <c r="B9" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129769237</v>
       </c>
       <c r="B10" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129769876</v>
+        <v>125580939</v>
       </c>
       <c r="B2" t="n">
-        <v>58113</v>
+        <v>58129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102623</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,29 +703,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>En route, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511585</v>
+        <v>511475</v>
       </c>
       <c r="R2" t="n">
-        <v>6294488</v>
+        <v>6294583</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +742,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:56</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,26 +772,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Nils Abrahamsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mattias Finndin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
-        </is>
-      </c>
+          <t>Nils Abrahamsson, Björn Gustafsson, Carl Lamm</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129769234</v>
+        <v>129769232</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511589</v>
+        <v>511608</v>
       </c>
       <c r="R3" t="n">
-        <v>6294556</v>
+        <v>6294473</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -874,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129769242</v>
+        <v>129769233</v>
       </c>
       <c r="B4" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,19 +939,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511511</v>
+        <v>511645</v>
       </c>
       <c r="R4" t="n">
-        <v>6294377</v>
+        <v>6294488</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -994,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129769878</v>
+        <v>129769234</v>
       </c>
       <c r="B5" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511624</v>
+        <v>511589</v>
       </c>
       <c r="R5" t="n">
-        <v>6294438</v>
+        <v>6294556</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1109,22 +1098,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129769880</v>
+        <v>129769237</v>
       </c>
       <c r="B6" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,14 +1184,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bommerås, Sm</t>
+          <t>Skruvaflyet, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511515</v>
+        <v>511527</v>
       </c>
       <c r="R6" t="n">
-        <v>6294373</v>
+        <v>6294529</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1229,22 +1218,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129769232</v>
+        <v>129769242</v>
       </c>
       <c r="B7" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,14 +1304,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skruvaflyet, Sm</t>
+          <t>Bommerås, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511608</v>
+        <v>511511</v>
       </c>
       <c r="R7" t="n">
-        <v>6294473</v>
+        <v>6294377</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1354,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1353,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129769866</v>
+        <v>129769856</v>
       </c>
       <c r="B8" t="n">
-        <v>58421</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,16 +1395,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1425,7 +1414,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1439,10 +1428,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511622</v>
+        <v>511711</v>
       </c>
       <c r="R8" t="n">
-        <v>6294525</v>
+        <v>6294477</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1474,7 +1463,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1473,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>06:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129769233</v>
+        <v>129769876</v>
       </c>
       <c r="B9" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1539,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1559,7 +1548,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511645</v>
+        <v>511585</v>
       </c>
       <c r="R9" t="n">
         <v>6294488</v>
@@ -1589,22 +1578,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>05:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129769237</v>
+        <v>129769878</v>
       </c>
       <c r="B10" t="n">
-        <v>58113</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511527</v>
+        <v>511624</v>
       </c>
       <c r="R10" t="n">
-        <v>6294529</v>
+        <v>6294438</v>
       </c>
       <c r="S10" t="n">
         <v>2</v>
@@ -1709,22 +1698,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,6 +1737,486 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129769880</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bommerås, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>511515</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6294373</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129769866</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skruvaflyet, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>511622</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6294525</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129769240</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skruvaflyet, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>511447</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6294491</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129769870</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skruvaflyet, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>511483</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6294559</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hovmantorp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>

--- a/artfynd/A 52544-2025 artfynd.xlsx
+++ b/artfynd/A 52544-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125580939</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769232</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769233</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769234</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769237</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,6 +1411,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769242</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769856</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769876</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1741,6 +1786,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769878</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1861,6 +1911,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769880</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1981,6 +2036,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769866</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2101,6 +2161,11 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769240</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2221,8 +2286,28 @@
           <t>Alight AB - NVI och fågelinventering Hovmantorrp</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129769870</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>